--- a/latex/tabs/algorithm_comparison.xlsx
+++ b/latex/tabs/algorithm_comparison.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -500,16 +500,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7752387063084751</v>
+        <v>0.7785668259574151</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6266577817257487</v>
+        <v>0.6284678283403711</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6011468315682151</v>
+        <v>0.6061720817216799</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5128983057969383</v>
+        <v>0.506355236236821</v>
       </c>
     </row>
     <row r="5">
@@ -519,16 +519,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7513797956365811</v>
+        <v>0.7513082874111404</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5991559132424696</v>
+        <v>0.5992514557717208</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5647999848990741</v>
+        <v>0.56470932030174</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5105079784694977</v>
+        <v>0.5160281241267252</v>
       </c>
     </row>
   </sheetData>

--- a/latex/tabs/algorithm_comparison.xlsx
+++ b/latex/tabs/algorithm_comparison.xlsx
@@ -458,20 +458,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BaselineOnly</t>
+          <t>SVD</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7492012818406858</v>
+        <v>0.6571</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6036991240262529</v>
+        <v>0.5286999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5614235123496866</v>
+        <v>0.4319</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5101231898504396</v>
+        <v>0.5436</v>
       </c>
     </row>
     <row r="3">
@@ -481,54 +481,54 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9288444549060079</v>
+        <v>1.181</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8103420761955668</v>
+        <v>0.9747</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8627530273104528</v>
+        <v>1.3948</v>
       </c>
       <c r="E3" t="n">
-        <v>0.437115674340361</v>
+        <v>0.5568</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NMF</t>
+          <t>BaselineOnly</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7785668259574151</v>
+        <v>0.6552</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6284678283403711</v>
+        <v>0.538</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6061720817216799</v>
+        <v>0.4293</v>
       </c>
       <c r="E4" t="n">
-        <v>0.506355236236821</v>
+        <v>0.5686</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SVD</t>
+          <t>NMF</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7513082874111404</v>
+        <v>0.8391999999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5992514557717208</v>
+        <v>0.6342</v>
       </c>
       <c r="D5" t="n">
-        <v>0.56470932030174</v>
+        <v>0.7043</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5160281241267252</v>
+        <v>0.4964</v>
       </c>
     </row>
   </sheetData>
